--- a/artfynd/A 14760-2026 artfynd.xlsx
+++ b/artfynd/A 14760-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>68386958</v>
       </c>
       <c r="B2" t="n">
-        <v>96254</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99038</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -711,10 +706,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454974.1659099626</v>
+        <v>454974</v>
       </c>
       <c r="R2" t="n">
-        <v>6562095.878265376</v>
+        <v>6562096</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -744,19 +739,9 @@
           <t>2017-06-27</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2017-06-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,6 +775,130 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>126245658</v>
+      </c>
+      <c r="B3" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Dammen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>455002</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6562170</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Kristinehamn</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Visnum</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ett tjugotal stänglar på östra sidan vägen i ytterslänt</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Åsa Tengström</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Åsa Tengström</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
         <is>
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>

--- a/artfynd/A 14760-2026 artfynd.xlsx
+++ b/artfynd/A 14760-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68386958</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -903,8 +913,17 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126245658</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>